--- a/data/raw/inventory/Week 33/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>18</v>
@@ -4379,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F104" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" t="n">
         <v>4</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>1</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F113" t="n">
         <v>14</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L113" t="n">
         <v>2</v>
@@ -11683,7 +11683,7 @@
         <v>408</v>
       </c>
       <c r="F182" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G182" t="n">
         <v>300</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K182" t="n">
         <v>408</v>
@@ -12427,7 +12427,7 @@
         <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -12439,7 +12439,7 @@
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
